--- a/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
+++ b/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
@@ -441,7 +441,7 @@
     <t>certificabile</t>
   </si>
   <si>
-    <t>(decodifica ANSC_29)</t>
+    <t>ID del Comune di Iscrizione AIRE (per gli intestatari AIRE, le notifiche anagrafiche verranno generate solo se questo campo è stato indicato e tale comune ha aderito ad ANSC)</t>
   </si>
   <si>
     <t>datiRiconoscimento</t>

--- a/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
+++ b/docs/Caratteristiche_servizi/Tracciato-Evento.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4588" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4596" uniqueCount="1438">
   <si>
     <t>Campo</t>
   </si>
@@ -1727,10 +1727,10 @@
     <t>officianteEventoUnioneCivile</t>
   </si>
   <si>
-    <t>Gianni Rossi Bürgermeister</t>
-  </si>
-  <si>
-    <t>Officiante che ha celebrato unione civile</t>
+    <t>Gianni Rossi Sindaco</t>
+  </si>
+  <si>
+    <t>Officiante che ha celebrato l'unione civile.</t>
   </si>
   <si>
     <t>Testo libero per modifica accordo (formula 121-septies.1)</t>
@@ -3377,6 +3377,21 @@
     <t>Tipo di modifica al matrimonio (decodifica ANSC_128)</t>
   </si>
   <si>
+    <t>sessoPrima</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>sesso prima della rettifica</t>
+  </si>
+  <si>
+    <t>sessoDopo</t>
+  </si>
+  <si>
+    <t>sesso dopo della rettifica</t>
+  </si>
+  <si>
     <t>idComune</t>
   </si>
   <si>
@@ -4131,12 +4146,6 @@
   </si>
   <si>
     <t>Data alla quale viene effettuata l'unione civile</t>
-  </si>
-  <si>
-    <t>Gianni Rossi Sindaco</t>
-  </si>
-  <si>
-    <t>Officiante che ha celebrato l'unione civile.</t>
   </si>
   <si>
     <t>tipoProvvedimentoScioglimento</t>
@@ -4357,9 +4366,6 @@
   </si>
   <si>
     <t>nuovoSesso</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
   <si>
     <t>nuovo sesso dell'intestatario</t>
@@ -10206,30 +10212,30 @@
     </row>
     <row r="13">
       <c r="A13" s="62" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="B13" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="62" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B14" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15">
@@ -16681,7 +16687,7 @@
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16822,6 +16828,34 @@
       </c>
       <c r="D10" s="144" t="s">
         <v>1084</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="144" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B11" s="144" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="144" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D11" s="144" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="144" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B12" s="144" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="144" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D12" s="144" t="s">
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -16854,7 +16888,7 @@
     </row>
     <row r="2">
       <c r="A2" s="146" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="B2" s="146" t="s">
         <v>5</v>
@@ -16863,12 +16897,12 @@
         <v>66</v>
       </c>
       <c r="D2" s="146" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="146" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="B3" s="146" t="s">
         <v>5</v>
@@ -16877,12 +16911,12 @@
         <v>69</v>
       </c>
       <c r="D3" s="146" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="146" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="146" t="s">
         <v>5</v>
@@ -16891,12 +16925,12 @@
         <v>72</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="146" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="B5" s="146" t="s">
         <v>5</v>
@@ -16905,12 +16939,12 @@
         <v>72</v>
       </c>
       <c r="D5" s="146" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="146" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="B6" s="146" t="s">
         <v>5</v>
@@ -16919,12 +16953,12 @@
         <v>623</v>
       </c>
       <c r="D6" s="146" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="146" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="B7" s="146" t="s">
         <v>5</v>
@@ -16933,7 +16967,7 @@
         <v>626</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="8">
@@ -16947,7 +16981,7 @@
         <v>343</v>
       </c>
       <c r="D8" s="146" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="9">
@@ -16961,21 +16995,21 @@
         <v>346</v>
       </c>
       <c r="D9" s="146" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="146" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="B10" s="146" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="146" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D10" s="146" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="11">
@@ -17032,7 +17066,7 @@
     </row>
     <row r="3">
       <c r="A3" s="148" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>5</v>
@@ -17041,12 +17075,12 @@
         <v>753</v>
       </c>
       <c r="D3" s="148" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="148" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="148" t="s">
         <v>5</v>
@@ -17055,12 +17089,12 @@
         <v>733</v>
       </c>
       <c r="D4" s="148" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="B5" s="148" t="s">
         <v>5</v>
@@ -17069,7 +17103,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6">
@@ -17083,12 +17117,12 @@
         <v>15</v>
       </c>
       <c r="D6" s="148" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="148" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="B7" s="148" t="s">
         <v>5</v>
@@ -17097,12 +17131,12 @@
         <v>849</v>
       </c>
       <c r="D7" s="148" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="148" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="B8" s="148" t="s">
         <v>5</v>
@@ -17111,7 +17145,7 @@
         <v>940</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="9">
@@ -17144,7 +17178,7 @@
     </row>
     <row r="11">
       <c r="A11" s="148" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="B11" s="148" t="s">
         <v>5</v>
@@ -17153,12 +17187,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="148" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="B12" s="148" t="s">
         <v>5</v>
@@ -17167,7 +17201,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="13">
@@ -17186,7 +17220,7 @@
     </row>
     <row r="14">
       <c r="A14" s="148" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B14" s="148" t="s">
         <v>5</v>
@@ -17195,7 +17229,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="148" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="15">
@@ -17209,21 +17243,21 @@
         <v>445</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="148" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="B16" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="148" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="D16" s="148" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="17">
@@ -17284,7 +17318,7 @@
     </row>
     <row r="21">
       <c r="A21" s="148" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B21" s="148" t="s">
         <v>5</v>
@@ -17293,7 +17327,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="148" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="22">
@@ -17312,7 +17346,7 @@
     </row>
     <row r="23">
       <c r="A23" s="148" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="B23" s="148" t="s">
         <v>59</v>
@@ -17321,15 +17355,15 @@
         <v>60</v>
       </c>
       <c r="D23" s="148" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="148" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="B24" s="148" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="C24" s="148" t="s">
         <v>64</v>
@@ -17340,10 +17374,10 @@
     </row>
     <row r="25">
       <c r="A25" s="148" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="B25" s="148" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="C25" s="148" t="s">
         <v>64</v>
@@ -17354,7 +17388,7 @@
     </row>
     <row r="26">
       <c r="A26" s="148" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="B26" s="148" t="s">
         <v>59</v>
@@ -17363,12 +17397,12 @@
         <v>60</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="148" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="B27" s="148" t="s">
         <v>59</v>
@@ -17377,7 +17411,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="28">
@@ -17396,7 +17430,7 @@
     </row>
     <row r="29">
       <c r="A29" s="148" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="B29" s="148" t="s">
         <v>59</v>
@@ -17405,12 +17439,12 @@
         <v>60</v>
       </c>
       <c r="D29" s="148" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="148" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="B30" s="148" t="s">
         <v>59</v>
@@ -17419,7 +17453,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="148" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="31">
@@ -17438,7 +17472,7 @@
     </row>
     <row r="32">
       <c r="A32" s="148" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="B32" s="148" t="s">
         <v>59</v>
@@ -17447,7 +17481,7 @@
         <v>60</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="33">
@@ -17466,7 +17500,7 @@
     </row>
     <row r="34">
       <c r="A34" s="148" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="B34" s="148" t="s">
         <v>5</v>
@@ -17475,12 +17509,12 @@
         <v>15</v>
       </c>
       <c r="D34" s="148" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="148" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="B35" s="148" t="s">
         <v>5</v>
@@ -17489,12 +17523,12 @@
         <v>27</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="148" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="B36" s="148" t="s">
         <v>59</v>
@@ -17503,7 +17537,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="148" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="37">
@@ -17553,7 +17587,7 @@
         <v>412</v>
       </c>
       <c r="B40" s="148" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="C40" s="148" t="s">
         <v>64</v>
@@ -17592,7 +17626,7 @@
     </row>
     <row r="43">
       <c r="A43" s="148" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="B43" s="148" t="s">
         <v>59</v>
@@ -17601,7 +17635,7 @@
         <v>99</v>
       </c>
       <c r="D43" s="148" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="44">
@@ -17615,12 +17649,12 @@
         <v>415</v>
       </c>
       <c r="D44" s="148" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="148" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="B45" s="148" t="s">
         <v>59</v>
@@ -17629,7 +17663,7 @@
         <v>99</v>
       </c>
       <c r="D45" s="148" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="46">
@@ -17648,21 +17682,21 @@
     </row>
     <row r="47">
       <c r="A47" s="148" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="B47" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="148" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="D47" s="148" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="148" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B48" s="148" t="s">
         <v>5</v>
@@ -17671,26 +17705,26 @@
         <v>567</v>
       </c>
       <c r="D48" s="148" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="148" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="B49" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="148" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="D49" s="148" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="148" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="B50" s="148" t="s">
         <v>5</v>
@@ -17699,26 +17733,26 @@
         <v>620</v>
       </c>
       <c r="D50" s="148" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="148" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="B51" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="148" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="D51" s="148" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="148" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="B52" s="148" t="s">
         <v>5</v>
@@ -17727,12 +17761,12 @@
         <v>626</v>
       </c>
       <c r="D52" s="148" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="148" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="B53" s="148" t="s">
         <v>5</v>
@@ -17741,18 +17775,18 @@
         <v>834</v>
       </c>
       <c r="D53" s="148" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="148" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="B54" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="148" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="D54" s="148" t="s">
         <v>703</v>
@@ -17760,16 +17794,16 @@
     </row>
     <row r="55">
       <c r="A55" s="148" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="B55" s="148" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="148" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="D55" s="148" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="56">
@@ -17788,7 +17822,7 @@
     </row>
     <row r="57">
       <c r="A57" s="148" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="B57" s="148" t="s">
         <v>5</v>
@@ -17797,12 +17831,12 @@
         <v>64</v>
       </c>
       <c r="D57" s="148" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="148" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="B58" s="148" t="s">
         <v>59</v>
@@ -17811,12 +17845,12 @@
         <v>99</v>
       </c>
       <c r="D58" s="148" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="148" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="B59" s="148" t="s">
         <v>5</v>
@@ -17825,7 +17859,7 @@
         <v>15</v>
       </c>
       <c r="D59" s="148" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="60">
@@ -17839,7 +17873,7 @@
         <v>64</v>
       </c>
       <c r="D60" s="148" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="61">
@@ -17853,7 +17887,7 @@
         <v>64</v>
       </c>
       <c r="D61" s="148" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="62">
@@ -17861,7 +17895,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="148" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="C62" s="148" t="s">
         <v>64</v>
@@ -17892,15 +17926,15 @@
         <v>5</v>
       </c>
       <c r="C64" s="148" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="D64" s="148" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="148" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="B65" s="148" t="s">
         <v>59</v>
@@ -17909,7 +17943,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="148" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="66">
@@ -17931,7 +17965,7 @@
         <v>429</v>
       </c>
       <c r="B67" s="148" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C67" s="148" t="s">
         <v>64</v>
@@ -17945,7 +17979,7 @@
         <v>431</v>
       </c>
       <c r="B68" s="148" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C68" s="148" t="s">
         <v>64</v>
@@ -17956,7 +17990,7 @@
     </row>
     <row r="69">
       <c r="A69" s="148" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="B69" s="148" t="s">
         <v>5</v>
@@ -17965,12 +17999,12 @@
         <v>27</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="148" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="B70" s="148" t="s">
         <v>5</v>
@@ -17979,7 +18013,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="148" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="71">
@@ -18162,7 +18196,7 @@
     </row>
     <row r="3">
       <c r="A3" s="150" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="B3" s="150" t="s">
         <v>5</v>
@@ -18171,12 +18205,12 @@
         <v>753</v>
       </c>
       <c r="D3" s="150" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="150" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="150" t="s">
         <v>5</v>
@@ -18185,12 +18219,12 @@
         <v>733</v>
       </c>
       <c r="D4" s="150" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="150" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="B5" s="150" t="s">
         <v>5</v>
@@ -18199,7 +18233,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="150" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6">
@@ -18213,12 +18247,12 @@
         <v>834</v>
       </c>
       <c r="D6" s="150" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="150" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="B7" s="150" t="s">
         <v>5</v>
@@ -18227,21 +18261,21 @@
         <v>15</v>
       </c>
       <c r="D7" s="150" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="150" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="B8" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="150" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="D8" s="150" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="9">
@@ -18260,7 +18294,7 @@
     </row>
     <row r="10">
       <c r="A10" s="150" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="B10" s="150" t="s">
         <v>5</v>
@@ -18269,12 +18303,12 @@
         <v>849</v>
       </c>
       <c r="D10" s="150" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="150" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="B11" s="150" t="s">
         <v>5</v>
@@ -18283,15 +18317,15 @@
         <v>940</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="150" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="C12" s="150" t="s">
         <v>64</v>
@@ -18302,10 +18336,10 @@
     </row>
     <row r="13">
       <c r="A13" s="150" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="C13" s="150" t="s">
         <v>64</v>
@@ -18316,7 +18350,7 @@
     </row>
     <row r="14">
       <c r="A14" s="150" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="B14" s="150" t="s">
         <v>5</v>
@@ -18325,7 +18359,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="150" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="15">
@@ -18344,7 +18378,7 @@
     </row>
     <row r="16">
       <c r="A16" s="150" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="B16" s="150" t="s">
         <v>5</v>
@@ -18353,7 +18387,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="150" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="17">
@@ -18372,16 +18406,16 @@
     </row>
     <row r="18">
       <c r="A18" s="150" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="B18" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="150" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="D18" s="150" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="19">
@@ -18442,7 +18476,7 @@
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B23" s="150" t="s">
         <v>5</v>
@@ -18451,7 +18485,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="150" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="24">
@@ -18498,7 +18532,7 @@
     </row>
     <row r="27">
       <c r="A27" s="150" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="B27" s="150" t="s">
         <v>59</v>
@@ -18507,7 +18541,7 @@
         <v>60</v>
       </c>
       <c r="D27" s="150" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="28">
@@ -18526,7 +18560,7 @@
     </row>
     <row r="29">
       <c r="A29" s="150" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="B29" s="150" t="s">
         <v>59</v>
@@ -18535,7 +18569,7 @@
         <v>60</v>
       </c>
       <c r="D29" s="150" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="30">
@@ -18585,7 +18619,7 @@
         <v>412</v>
       </c>
       <c r="B33" s="150" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="C33" s="150" t="s">
         <v>64</v>
@@ -18596,7 +18630,7 @@
     </row>
     <row r="34">
       <c r="A34" s="150" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="B34" s="150" t="s">
         <v>59</v>
@@ -18605,7 +18639,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="150" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="35">
@@ -18624,7 +18658,7 @@
     </row>
     <row r="36">
       <c r="A36" s="150" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B36" s="150" t="s">
         <v>59</v>
@@ -18633,7 +18667,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="150" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="37">
@@ -18652,77 +18686,77 @@
     </row>
     <row r="38">
       <c r="A38" s="150" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="B38" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="150" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="D38" s="150" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="150" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B39" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="150" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="D39" s="150" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="150" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="B40" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="150" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="D40" s="150" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="150" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="B41" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="150" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="D41" s="150" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="150" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="B42" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="150" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="D42" s="150" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="150" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="B43" s="150" t="s">
         <v>5</v>
@@ -18731,12 +18765,12 @@
         <v>626</v>
       </c>
       <c r="D43" s="150" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="150" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="B44" s="150" t="s">
         <v>5</v>
@@ -18745,18 +18779,18 @@
         <v>834</v>
       </c>
       <c r="D44" s="150" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="150" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="B45" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="150" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="D45" s="150" t="s">
         <v>703</v>
@@ -18764,16 +18798,16 @@
     </row>
     <row r="46">
       <c r="A46" s="150" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="B46" s="150" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="150" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="D46" s="150" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="47">
@@ -18801,7 +18835,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="150" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="49">
@@ -18809,7 +18843,7 @@
         <v>429</v>
       </c>
       <c r="B49" s="150" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C49" s="150" t="s">
         <v>64</v>
@@ -18823,7 +18857,7 @@
         <v>431</v>
       </c>
       <c r="B50" s="150" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C50" s="150" t="s">
         <v>64</v>
@@ -18834,7 +18868,7 @@
     </row>
     <row r="51">
       <c r="A51" s="150" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B51" s="150" t="s">
         <v>5</v>
@@ -18843,7 +18877,7 @@
         <v>27</v>
       </c>
       <c r="D51" s="150" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="52">
@@ -18851,7 +18885,7 @@
         <v>466</v>
       </c>
       <c r="B52" s="150" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C52" s="150" t="s">
         <v>64</v>
@@ -18886,35 +18920,35 @@
     </row>
     <row r="2">
       <c r="A2" s="152" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="152" t="s">
         <v>1220</v>
       </c>
-      <c r="B2" s="152" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="152" t="s">
-        <v>1215</v>
-      </c>
       <c r="D2" s="152" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="152" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="152" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="152" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="B4" s="152" t="s">
         <v>5</v>
@@ -18923,35 +18957,35 @@
         <v>15</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="152" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="B5" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="152" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="152" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B6" s="152" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="152" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D6" s="152" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -18980,7 +19014,7 @@
     </row>
     <row r="2">
       <c r="A2" s="154" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="154" t="s">
         <v>5</v>
@@ -18989,12 +19023,12 @@
         <v>72</v>
       </c>
       <c r="D2" s="154" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="154" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="B3" s="154" t="s">
         <v>5</v>
@@ -19003,12 +19037,12 @@
         <v>75</v>
       </c>
       <c r="D3" s="154" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="154" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="B4" s="154" t="s">
         <v>5</v>
@@ -19017,12 +19051,12 @@
         <v>66</v>
       </c>
       <c r="D4" s="154" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="154" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="B5" s="154" t="s">
         <v>5</v>
@@ -19031,40 +19065,40 @@
         <v>69</v>
       </c>
       <c r="D5" s="154" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="154" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="B6" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="154" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="D6" s="154" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="154" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="B7" s="154" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="154" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D7" s="154" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="154" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="B8" s="154" t="s">
         <v>5</v>
@@ -19078,7 +19112,7 @@
     </row>
     <row r="9">
       <c r="A9" s="154" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="B9" s="154" t="s">
         <v>5</v>
@@ -19144,7 +19178,7 @@
     </row>
     <row r="2">
       <c r="A2" s="156" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="B2" s="156" t="s">
         <v>5</v>
@@ -19153,12 +19187,12 @@
         <v>15</v>
       </c>
       <c r="D2" s="156" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="156" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="B3" s="156" t="s">
         <v>59</v>
@@ -19167,12 +19201,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="156" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="156" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="B4" s="156" t="s">
         <v>5</v>
@@ -19181,12 +19215,12 @@
         <v>940</v>
       </c>
       <c r="D4" s="156" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="156" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="B5" s="156" t="s">
         <v>5</v>
@@ -19195,7 +19229,7 @@
         <v>849</v>
       </c>
       <c r="D5" s="156" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6">
@@ -19214,16 +19248,16 @@
     </row>
     <row r="7">
       <c r="A7" s="156" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="B7" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="156" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="D7" s="156" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="8">
@@ -19237,7 +19271,7 @@
         <v>572</v>
       </c>
       <c r="D8" s="156" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="9">
@@ -19245,18 +19279,18 @@
         <v>569</v>
       </c>
       <c r="B9" s="156" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="C9" s="156" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="156" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="156" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="B10" s="156" t="s">
         <v>5</v>
@@ -19265,12 +19299,12 @@
         <v>15</v>
       </c>
       <c r="D10" s="156" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="156" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="B11" s="156" t="s">
         <v>5</v>
@@ -19279,26 +19313,26 @@
         <v>15</v>
       </c>
       <c r="D11" s="156" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="156" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="B12" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="156" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="D12" s="156" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="156" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="B13" s="156" t="s">
         <v>5</v>
@@ -19307,26 +19341,26 @@
         <v>15</v>
       </c>
       <c r="D13" s="156" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="156" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="B14" s="156" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="156" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="D14" s="156" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="156" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="B15" s="156" t="s">
         <v>59</v>
@@ -19335,7 +19369,7 @@
         <v>60</v>
       </c>
       <c r="D15" s="156" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
   </sheetData>
@@ -19448,16 +19482,16 @@
     </row>
     <row r="8">
       <c r="A8" s="158" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="B8" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="158" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="D8" s="158" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9">
@@ -19476,21 +19510,21 @@
     </row>
     <row r="10">
       <c r="A10" s="158" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="B10" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="158" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="D10" s="158" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="158" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B11" s="158" t="s">
         <v>5</v>
@@ -19499,21 +19533,21 @@
         <v>15</v>
       </c>
       <c r="D11" s="158" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="158" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="B12" s="158" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="158" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="D12" s="158" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
   </sheetData>
@@ -19594,7 +19628,7 @@
     </row>
     <row r="2">
       <c r="A2" s="160" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="B2" s="160" t="s">
         <v>5</v>
@@ -19603,7 +19637,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="160" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="3">
@@ -19617,12 +19651,12 @@
         <v>64</v>
       </c>
       <c r="D3" s="160" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="160" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="B4" s="160" t="s">
         <v>177</v>
@@ -19660,7 +19694,7 @@
     </row>
     <row r="2">
       <c r="A2" s="162" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="B2" s="162" t="s">
         <v>5</v>
@@ -19669,12 +19703,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="162" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="162" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B3" s="162" t="s">
         <v>59</v>
@@ -19683,12 +19717,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="162" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="162" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B4" s="162" t="s">
         <v>59</v>
@@ -19697,7 +19731,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="162" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="5">
@@ -19730,7 +19764,7 @@
     </row>
     <row r="7">
       <c r="A7" s="162" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="B7" s="162" t="s">
         <v>59</v>
@@ -19739,12 +19773,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="162" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="162" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="B8" s="162" t="s">
         <v>59</v>
@@ -19753,7 +19787,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="162" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="9">
@@ -19800,7 +19834,7 @@
     </row>
     <row r="12">
       <c r="A12" s="162" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="B12" s="162" t="s">
         <v>59</v>
@@ -19809,7 +19843,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="162" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="13">
@@ -19828,16 +19862,16 @@
     </row>
     <row r="14">
       <c r="A14" s="162" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="162" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15">
@@ -19898,21 +19932,21 @@
     </row>
     <row r="19">
       <c r="A19" s="162" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="B19" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="D19" s="162" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="162" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B20" s="162" t="s">
         <v>5</v>
@@ -19921,26 +19955,26 @@
         <v>15</v>
       </c>
       <c r="D20" s="162" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="162" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="B21" s="162" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="162" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="D21" s="162" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="162" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="B22" s="162" t="s">
         <v>5</v>
@@ -19949,7 +19983,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="23">
@@ -19982,7 +20016,7 @@
     </row>
     <row r="25">
       <c r="A25" s="162" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="B25" s="162" t="s">
         <v>59</v>
@@ -19991,7 +20025,7 @@
         <v>99</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="26">
@@ -20010,7 +20044,7 @@
     </row>
     <row r="27">
       <c r="A27" s="162" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="B27" s="162" t="s">
         <v>5</v>
@@ -20019,12 +20053,12 @@
         <v>64</v>
       </c>
       <c r="D27" s="162" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="162" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="B28" s="162" t="s">
         <v>59</v>
@@ -20033,7 +20067,7 @@
         <v>60</v>
       </c>
       <c r="D28" s="162" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -20062,7 +20096,7 @@
     </row>
     <row r="2">
       <c r="A2" s="164" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="B2" s="164" t="s">
         <v>5</v>
@@ -20071,12 +20105,12 @@
         <v>64</v>
       </c>
       <c r="D2" s="164" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="164" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B3" s="164" t="s">
         <v>59</v>
@@ -20085,12 +20119,12 @@
         <v>60</v>
       </c>
       <c r="D3" s="164" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="164" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B4" s="164" t="s">
         <v>59</v>
@@ -20099,7 +20133,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="164" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="5">
@@ -20132,7 +20166,7 @@
     </row>
     <row r="7">
       <c r="A7" s="164" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="B7" s="164" t="s">
         <v>59</v>
@@ -20141,12 +20175,12 @@
         <v>60</v>
       </c>
       <c r="D7" s="164" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="164" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="B8" s="164" t="s">
         <v>59</v>
@@ -20155,7 +20189,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="164" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="9">
@@ -20230,63 +20264,63 @@
     </row>
     <row r="14">
       <c r="A14" s="164" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B14" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D14" s="164" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="164" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="B15" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="164" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="D15" s="164" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="164" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B16" s="164" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="164" t="s">
         <v>1312</v>
       </c>
-      <c r="B16" s="164" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="164" t="s">
-        <v>1307</v>
-      </c>
       <c r="D16" s="164" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="164" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B17" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="164" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="D17" s="164" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="164" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="B18" s="164" t="s">
         <v>5</v>
@@ -20295,7 +20329,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="164" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="19">
@@ -20314,58 +20348,58 @@
     </row>
     <row r="20">
       <c r="A20" s="164" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="B20" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D20" s="164" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="164" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="B21" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="164" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="B22" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D22" s="164" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="164" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="B23" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D23" s="164" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="24">
@@ -20379,12 +20413,12 @@
         <v>378</v>
       </c>
       <c r="D24" s="164" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="164" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="B25" s="164" t="s">
         <v>5</v>
@@ -20393,21 +20427,21 @@
         <v>15</v>
       </c>
       <c r="D25" s="164" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="164" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="B26" s="164" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D26" s="164" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
     </row>
   </sheetData>
@@ -20450,7 +20484,7 @@
     </row>
     <row r="3">
       <c r="A3" s="166" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="B3" s="166" t="s">
         <v>5</v>
@@ -20459,7 +20493,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="166" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="4">
@@ -20478,7 +20512,7 @@
     </row>
     <row r="5">
       <c r="A5" s="166" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="B5" s="166" t="s">
         <v>5</v>
@@ -20487,7 +20521,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="166" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -20512,29 +20546,29 @@
         <v>5</v>
       </c>
       <c r="C7" s="166" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D7" s="166" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="166" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="B8" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="166" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D8" s="166" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="166" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="B9" s="166" t="s">
         <v>59</v>
@@ -20543,7 +20577,7 @@
         <v>60</v>
       </c>
       <c r="D9" s="166" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="10">
@@ -20562,7 +20596,7 @@
     </row>
     <row r="11">
       <c r="A11" s="166" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="B11" s="166" t="s">
         <v>5</v>
@@ -20571,12 +20605,12 @@
         <v>15</v>
       </c>
       <c r="D11" s="166" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="166" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="B12" s="166" t="s">
         <v>59</v>
@@ -20585,7 +20619,7 @@
         <v>99</v>
       </c>
       <c r="D12" s="166" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="13">
@@ -20604,7 +20638,7 @@
     </row>
     <row r="14">
       <c r="A14" s="166" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B14" s="166" t="s">
         <v>59</v>
@@ -20613,7 +20647,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="166" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="15">
@@ -20646,7 +20680,7 @@
     </row>
     <row r="17">
       <c r="A17" s="166" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B17" s="166" t="s">
         <v>59</v>
@@ -20655,12 +20689,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="166" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="166" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="B18" s="166" t="s">
         <v>59</v>
@@ -20669,12 +20703,12 @@
         <v>60</v>
       </c>
       <c r="D18" s="166" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="166" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="B19" s="166" t="s">
         <v>59</v>
@@ -20683,7 +20717,7 @@
         <v>60</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="20">
@@ -20716,16 +20750,16 @@
     </row>
     <row r="22">
       <c r="A22" s="166" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="B22" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="166" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="D22" s="166" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="23">
@@ -20744,7 +20778,7 @@
     </row>
     <row r="24">
       <c r="A24" s="166" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="B24" s="166" t="s">
         <v>59</v>
@@ -20753,7 +20787,7 @@
         <v>99</v>
       </c>
       <c r="D24" s="166" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="25">
@@ -20772,16 +20806,16 @@
     </row>
     <row r="26">
       <c r="A26" s="166" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="B26" s="166" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="166" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="D26" s="166" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="27">
@@ -20806,10 +20840,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="166" t="s">
-        <v>1343</v>
+        <v>541</v>
       </c>
       <c r="D28" s="166" t="s">
-        <v>1344</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29">
@@ -20828,7 +20862,7 @@
     </row>
     <row r="30">
       <c r="A30" s="166" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="B30" s="166" t="s">
         <v>5</v>
@@ -20837,7 +20871,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="166" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="31">
@@ -20856,7 +20890,7 @@
     </row>
     <row r="32">
       <c r="A32" s="166" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="B32" s="166" t="s">
         <v>59</v>
@@ -20865,7 +20899,7 @@
         <v>60</v>
       </c>
       <c r="D32" s="166" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="33">
@@ -20908,7 +20942,7 @@
     </row>
     <row r="2">
       <c r="A2" s="168" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="B2" s="168" t="s">
         <v>5</v>
@@ -20917,7 +20951,7 @@
         <v>64</v>
       </c>
       <c r="D2" s="168" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="3">
@@ -20950,7 +20984,7 @@
     </row>
     <row r="5">
       <c r="A5" s="168" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="B5" s="168" t="s">
         <v>5</v>
@@ -20959,7 +20993,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="168" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6">
@@ -20970,24 +21004,24 @@
         <v>5</v>
       </c>
       <c r="C6" s="168" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="D6" s="168" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="168" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B7" s="168" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="168" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="D7" s="168" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="8">
@@ -21050,10 +21084,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="170" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D3" s="170" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
   </sheetData>
@@ -21102,7 +21136,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="172" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="D3" s="172" t="s">
         <v>550</v>
@@ -21110,7 +21144,7 @@
     </row>
     <row r="4">
       <c r="A4" s="172" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="B4" s="172" t="s">
         <v>5</v>
@@ -21119,7 +21153,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="172" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
   </sheetData>
@@ -21137,7 +21171,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="174" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21162,16 +21196,16 @@
     </row>
     <row r="3">
       <c r="A3" s="174" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B3" s="174" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="174" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="D3" s="174" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="4">
@@ -21182,10 +21216,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="174" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="D4" s="174" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="5">
@@ -21196,10 +21230,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="174" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="D5" s="174" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="6">
@@ -21227,7 +21261,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="174" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="8">
@@ -21241,12 +21275,12 @@
         <v>64</v>
       </c>
       <c r="D8" s="174" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="174" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B9" s="174" t="s">
         <v>235</v>
@@ -21269,7 +21303,7 @@
         <v>64</v>
       </c>
       <c r="D10" s="174" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="11">
@@ -21403,7 +21437,7 @@
         <v>151</v>
       </c>
       <c r="B20" s="174" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="C20" s="174" t="s">
         <v>64</v>
@@ -21417,7 +21451,7 @@
         <v>153</v>
       </c>
       <c r="B21" s="174" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="C21" s="174" t="s">
         <v>64</v>
@@ -21431,7 +21465,7 @@
         <v>155</v>
       </c>
       <c r="B22" s="174" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="C22" s="174" t="s">
         <v>64</v>
@@ -21445,7 +21479,7 @@
         <v>157</v>
       </c>
       <c r="B23" s="174" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="C23" s="174" t="s">
         <v>64</v>
@@ -21459,7 +21493,7 @@
         <v>159</v>
       </c>
       <c r="B24" s="174" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="C24" s="174" t="s">
         <v>64</v>
@@ -21473,7 +21507,7 @@
         <v>161</v>
       </c>
       <c r="B25" s="174" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="C25" s="174" t="s">
         <v>64</v>
@@ -21487,7 +21521,7 @@
         <v>207</v>
       </c>
       <c r="B26" s="174" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="C26" s="174" t="s">
         <v>64</v>
@@ -21501,7 +21535,7 @@
         <v>163</v>
       </c>
       <c r="B27" s="174" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="C27" s="174" t="s">
         <v>64</v>
@@ -21515,7 +21549,7 @@
         <v>165</v>
       </c>
       <c r="B28" s="174" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="C28" s="174" t="s">
         <v>64</v>
@@ -21529,7 +21563,7 @@
         <v>167</v>
       </c>
       <c r="B29" s="174" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C29" s="174" t="s">
         <v>64</v>
@@ -21543,7 +21577,7 @@
         <v>169</v>
       </c>
       <c r="B30" s="174" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C30" s="174" t="s">
         <v>64</v>
@@ -21557,7 +21591,7 @@
         <v>170</v>
       </c>
       <c r="B31" s="174" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C31" s="174" t="s">
         <v>64</v>
@@ -21613,7 +21647,7 @@
         <v>179</v>
       </c>
       <c r="B35" s="174" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="C35" s="174" t="s">
         <v>64</v>
@@ -21627,7 +21661,7 @@
         <v>181</v>
       </c>
       <c r="B36" s="174" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="C36" s="174" t="s">
         <v>64</v>
@@ -21641,7 +21675,7 @@
         <v>183</v>
       </c>
       <c r="B37" s="174" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="C37" s="174" t="s">
         <v>64</v>
@@ -21655,7 +21689,7 @@
         <v>185</v>
       </c>
       <c r="B38" s="174" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="C38" s="174" t="s">
         <v>64</v>
@@ -21669,7 +21703,7 @@
         <v>187</v>
       </c>
       <c r="B39" s="174" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C39" s="174" t="s">
         <v>64</v>
@@ -21683,7 +21717,7 @@
         <v>189</v>
       </c>
       <c r="B40" s="174" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="C40" s="174" t="s">
         <v>64</v>
@@ -21697,7 +21731,7 @@
         <v>191</v>
       </c>
       <c r="B41" s="174" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C41" s="174" t="s">
         <v>64</v>
@@ -21711,7 +21745,7 @@
         <v>193</v>
       </c>
       <c r="B42" s="174" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="C42" s="174" t="s">
         <v>64</v>
@@ -21725,7 +21759,7 @@
         <v>195</v>
       </c>
       <c r="B43" s="174" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="C43" s="174" t="s">
         <v>64</v>
@@ -21739,7 +21773,7 @@
         <v>197</v>
       </c>
       <c r="B44" s="174" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="C44" s="174" t="s">
         <v>64</v>
@@ -21781,7 +21815,7 @@
         <v>226</v>
       </c>
       <c r="B47" s="174" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="C47" s="174" t="s">
         <v>64</v>
@@ -21795,7 +21829,7 @@
         <v>211</v>
       </c>
       <c r="B48" s="174" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="C48" s="174" t="s">
         <v>64</v>
@@ -21851,7 +21885,7 @@
         <v>244</v>
       </c>
       <c r="B52" s="174" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="C52" s="174" t="s">
         <v>64</v>
@@ -21865,7 +21899,7 @@
         <v>204</v>
       </c>
       <c r="B53" s="174" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="C53" s="174" t="s">
         <v>64</v>
@@ -21879,7 +21913,7 @@
         <v>242</v>
       </c>
       <c r="B54" s="174" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="C54" s="174" t="s">
         <v>64</v>
@@ -21906,7 +21940,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -21959,7 +21993,7 @@
     </row>
     <row r="5">
       <c r="A5" s="176" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="B5" s="176" t="s">
         <v>134</v>
@@ -21968,12 +22002,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="176" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="176" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="B6" s="176" t="s">
         <v>134</v>
@@ -21982,12 +22016,12 @@
         <v>15</v>
       </c>
       <c r="D6" s="176" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="176" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B7" s="176" t="s">
         <v>5</v>
@@ -21996,12 +22030,12 @@
         <v>849</v>
       </c>
       <c r="D7" s="176" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="176" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="B8" s="176" t="s">
         <v>5</v>
@@ -22010,7 +22044,7 @@
         <v>940</v>
       </c>
       <c r="D8" s="176" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="9">
@@ -22024,12 +22058,12 @@
         <v>849</v>
       </c>
       <c r="D9" s="176" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="176" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="B10" s="176" t="s">
         <v>5</v>
@@ -22038,12 +22072,12 @@
         <v>940</v>
       </c>
       <c r="D10" s="176" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="176" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="B11" s="176" t="s">
         <v>5</v>
@@ -22052,12 +22086,12 @@
         <v>849</v>
       </c>
       <c r="D11" s="176" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="176" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="B12" s="176" t="s">
         <v>5</v>
@@ -22066,12 +22100,12 @@
         <v>940</v>
       </c>
       <c r="D12" s="176" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="176" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B13" s="176" t="s">
         <v>5</v>
@@ -22080,12 +22114,12 @@
         <v>940</v>
       </c>
       <c r="D13" s="176" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="176" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B14" s="176" t="s">
         <v>5</v>
@@ -22094,7 +22128,7 @@
         <v>849</v>
       </c>
       <c r="D14" s="176" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="15">
@@ -22113,21 +22147,21 @@
     </row>
     <row r="16">
       <c r="A16" s="176" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="B16" s="176" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>1418</v>
+        <v>1092</v>
       </c>
       <c r="D16" s="176" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="176" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B17" s="176" t="s">
         <v>59</v>
@@ -22136,12 +22170,12 @@
         <v>60</v>
       </c>
       <c r="D17" s="176" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="176" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B18" s="176" t="s">
         <v>5</v>
@@ -22150,12 +22184,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="176" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="176" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B19" s="176" t="s">
         <v>128</v>
@@ -22164,12 +22198,12 @@
         <v>64</v>
       </c>
       <c r="D19" s="176" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="176" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B20" s="176" t="s">
         <v>134</v>
@@ -22178,7 +22212,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="176" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
   </sheetData>
@@ -22199,7 +22233,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -22238,7 +22272,7 @@
     </row>
     <row r="4">
       <c r="A4" s="178" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B4" s="178" t="s">
         <v>172</v>
@@ -22261,7 +22295,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="178" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6">
@@ -22280,7 +22314,7 @@
     </row>
     <row r="7">
       <c r="A7" s="178" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B7" s="178" t="s">
         <v>5</v>
@@ -22289,12 +22323,12 @@
         <v>940</v>
       </c>
       <c r="D7" s="178" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="178" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B8" s="178" t="s">
         <v>5</v>
@@ -22303,12 +22337,12 @@
         <v>849</v>
       </c>
       <c r="D8" s="178" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="178" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B9" s="178" t="s">
         <v>5</v>
@@ -22317,7 +22351,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="178" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
   </sheetData>
@@ -22432,7 +22466,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="180" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="C1" t="s">
         <v>64</v>
@@ -22471,7 +22505,7 @@
     </row>
     <row r="4">
       <c r="A4" s="180" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B4" s="180" t="s">
         <v>172</v>
@@ -22494,12 +22528,12 @@
         <v>15</v>
       </c>
       <c r="D5" s="180" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="180" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B6" s="180" t="s">
         <v>5</v>
@@ -22508,7 +22542,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="180" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
   </sheetData>
